--- a/psychopy_exp_files/sequences/localizer_conditions_things-meg_mixed_5cat_01.xlsx
+++ b/psychopy_exp_files/sequences/localizer_conditions_things-meg_mixed_5cat_01.xlsx
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -14964,12 +14964,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -15635,12 +15635,12 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -16383,12 +16383,12 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -17245,12 +17245,12 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -18115,12 +18115,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -18977,12 +18977,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -19343,12 +19343,12 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -19465,12 +19465,12 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -20831,12 +20831,12 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21385,7 +21385,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -22006,12 +22006,12 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -22441,12 +22441,12 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -22671,7 +22671,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -22685,12 +22685,12 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -24104,12 +24104,12 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -24769,7 +24769,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G394" t="n">
@@ -24783,12 +24783,12 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G397" t="n">
@@ -24966,12 +24966,12 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G420" t="n">
@@ -26377,12 +26377,12 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -26615,7 +26615,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G424" t="n">
@@ -26629,12 +26629,12 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G433" t="n">
@@ -27178,12 +27178,12 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G439" t="n">
@@ -27552,12 +27552,12 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -27782,7 +27782,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G443" t="n">
@@ -27796,12 +27796,12 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G453" t="n">
@@ -28414,12 +28414,12 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -28652,7 +28652,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G457" t="n">
@@ -28666,12 +28666,12 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G481" t="n">
@@ -30138,12 +30138,12 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G492" t="n">
@@ -30817,12 +30817,12 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -31047,7 +31047,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G496" t="n">
@@ -31061,7 +31061,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G507" t="n">
@@ -31740,12 +31740,12 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G513" t="n">
@@ -32114,12 +32114,12 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -32771,7 +32771,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G524" t="n">
@@ -32785,12 +32785,12 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -34129,7 +34129,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G546" t="n">
@@ -34143,7 +34143,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
@@ -34320,7 +34320,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G549" t="n">
@@ -34334,12 +34334,12 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -34503,7 +34503,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G552" t="n">
@@ -34517,12 +34517,12 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -34747,7 +34747,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G556" t="n">
@@ -34761,12 +34761,12 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G573" t="n">
@@ -35814,12 +35814,12 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
@@ -36227,7 +36227,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G580" t="n">
@@ -36241,12 +36241,12 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
@@ -37150,7 +37150,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -37164,12 +37164,12 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G603" t="n">
@@ -37660,12 +37660,12 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -38073,7 +38073,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -38087,12 +38087,12 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
@@ -38466,7 +38466,7 @@
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -39683,7 +39683,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G636" t="n">
@@ -39697,12 +39697,12 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G644" t="n">
@@ -40193,12 +40193,12 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -40484,7 +40484,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G649" t="n">
@@ -40498,12 +40498,12 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
